--- a/artfynd/A 21343-2022 artfynd.xlsx
+++ b/artfynd/A 21343-2022 artfynd.xlsx
@@ -1771,7 +1771,7 @@
         <v>136117263</v>
       </c>
       <c r="B11" t="n">
-        <v>57791</v>
+        <v>57793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
